--- a/feature description.xlsx
+++ b/feature description.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\annxy\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\多\uoft\IMI BIG DATA COMPETITION\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F315B459-9520-4B69-9C71-35A7BE683ADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36C10009-534D-4D49-80C2-96510AEEF0CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1007,9 +1007,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1018,6 +1015,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1319,75 +1319,75 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="10" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="7"/>
+      <c r="C3" s="10"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="7"/>
+      <c r="C4" s="10"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="7"/>
+      <c r="C5" s="10"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="7"/>
+      <c r="C6" s="10"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="7"/>
+      <c r="C7" s="10"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="7"/>
+      <c r="C8" s="10"/>
     </row>
     <row r="9" spans="1:3" ht="41.65" x14ac:dyDescent="0.4">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>74</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -1395,10 +1395,10 @@
       </c>
     </row>
     <row r="10" spans="1:3" ht="27.75" x14ac:dyDescent="0.4">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="3" t="s">
@@ -1406,10 +1406,10 @@
       </c>
     </row>
     <row r="11" spans="1:3" ht="27.75" x14ac:dyDescent="0.4">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="8" t="s">
         <v>59</v>
       </c>
       <c r="C11" s="3" t="s">
@@ -1417,75 +1417,75 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="10" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C13" s="7"/>
+      <c r="C13" s="10"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="7"/>
+      <c r="C14" s="10"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C15" s="7"/>
+      <c r="C15" s="10"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="7"/>
+      <c r="C16" s="10"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="C17" s="7"/>
+      <c r="C17" s="10"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="7"/>
+      <c r="C18" s="10"/>
     </row>
     <row r="19" spans="1:3" ht="41.65" x14ac:dyDescent="0.4">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="8" t="s">
         <v>75</v>
       </c>
       <c r="C19" s="3" t="s">
@@ -1493,10 +1493,10 @@
       </c>
     </row>
     <row r="20" spans="1:3" ht="27.75" x14ac:dyDescent="0.4">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="8" t="s">
         <v>76</v>
       </c>
       <c r="C20" s="3" t="s">
@@ -1504,10 +1504,10 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="27.75" x14ac:dyDescent="0.4">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="8" t="s">
         <v>79</v>
       </c>
       <c r="C21" s="3" t="s">
@@ -1515,75 +1515,75 @@
       </c>
     </row>
     <row r="22" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="10" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="C23" s="7"/>
+      <c r="C23" s="10"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="C24" s="7"/>
+      <c r="C24" s="10"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="C25" s="7"/>
+      <c r="C25" s="10"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A26" s="9" t="s">
+      <c r="A26" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="C26" s="7"/>
+      <c r="C26" s="10"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A27" s="9" t="s">
+      <c r="A27" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="C27" s="7"/>
+      <c r="C27" s="10"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A28" s="9" t="s">
+      <c r="A28" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="C28" s="7"/>
+      <c r="C28" s="10"/>
     </row>
     <row r="29" spans="1:3" ht="41.65" x14ac:dyDescent="0.4">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="8" t="s">
         <v>99</v>
       </c>
       <c r="C29" s="3" t="s">
@@ -1591,10 +1591,10 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="27.75" x14ac:dyDescent="0.4">
-      <c r="A30" s="9" t="s">
+      <c r="A30" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="8" t="s">
         <v>100</v>
       </c>
       <c r="C30" s="3" t="s">
@@ -1602,10 +1602,10 @@
       </c>
     </row>
     <row r="31" spans="1:3" ht="27.75" x14ac:dyDescent="0.4">
-      <c r="A31" s="9" t="s">
+      <c r="A31" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="8" t="s">
         <v>101</v>
       </c>
       <c r="C31" s="3" t="s">
@@ -1613,75 +1613,75 @@
       </c>
     </row>
     <row r="32" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="9" t="s">
+      <c r="A32" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="10" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A33" s="9" t="s">
+      <c r="A33" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="C33" s="7"/>
+      <c r="C33" s="10"/>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A34" s="9" t="s">
+      <c r="A34" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="C34" s="7"/>
+      <c r="C34" s="10"/>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A35" s="9" t="s">
+      <c r="A35" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="C35" s="7"/>
+      <c r="C35" s="10"/>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A36" s="9" t="s">
+      <c r="A36" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C36" s="7"/>
+      <c r="C36" s="10"/>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A37" s="9" t="s">
+      <c r="A37" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C37" s="7"/>
+      <c r="C37" s="10"/>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A38" s="9" t="s">
+      <c r="A38" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="C38" s="7"/>
+      <c r="C38" s="10"/>
     </row>
     <row r="39" spans="1:3" ht="60.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="9" t="s">
+      <c r="A39" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B39" s="9" t="s">
+      <c r="B39" s="8" t="s">
         <v>109</v>
       </c>
       <c r="C39" s="3" t="s">
@@ -1689,10 +1689,10 @@
       </c>
     </row>
     <row r="40" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="9" t="s">
+      <c r="A40" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="8" t="s">
         <v>110</v>
       </c>
       <c r="C40" s="3" t="s">
@@ -1700,10 +1700,10 @@
       </c>
     </row>
     <row r="41" spans="1:3" ht="27.75" x14ac:dyDescent="0.4">
-      <c r="A41" s="9" t="s">
+      <c r="A41" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="8" t="s">
         <v>111</v>
       </c>
       <c r="C41" s="3" t="s">
@@ -1711,75 +1711,75 @@
       </c>
     </row>
     <row r="42" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="9" t="s">
+      <c r="A42" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="9" t="s">
+      <c r="B42" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="C42" s="10" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A43" s="9" t="s">
+      <c r="A43" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="B43" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="C43" s="7"/>
+      <c r="C43" s="10"/>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A44" s="9" t="s">
+      <c r="A44" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="C44" s="7"/>
+      <c r="C44" s="10"/>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A45" s="9" t="s">
+      <c r="A45" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="9" t="s">
+      <c r="B45" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="C45" s="7"/>
+      <c r="C45" s="10"/>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A46" s="9" t="s">
+      <c r="A46" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B46" s="9" t="s">
+      <c r="B46" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="C46" s="7"/>
+      <c r="C46" s="10"/>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A47" s="9" t="s">
+      <c r="A47" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B47" s="9" t="s">
+      <c r="B47" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="C47" s="7"/>
+      <c r="C47" s="10"/>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A48" s="9" t="s">
+      <c r="A48" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B48" s="9" t="s">
+      <c r="B48" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="C48" s="7"/>
+      <c r="C48" s="10"/>
     </row>
     <row r="49" spans="1:3" ht="41.65" x14ac:dyDescent="0.4">
-      <c r="A49" s="9" t="s">
+      <c r="A49" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B49" s="9" t="s">
+      <c r="B49" s="8" t="s">
         <v>119</v>
       </c>
       <c r="C49" s="3" t="s">
@@ -1787,10 +1787,10 @@
       </c>
     </row>
     <row r="50" spans="1:3" ht="27.75" x14ac:dyDescent="0.4">
-      <c r="A50" s="9" t="s">
+      <c r="A50" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B50" s="9" t="s">
+      <c r="B50" s="8" t="s">
         <v>120</v>
       </c>
       <c r="C50" s="3" t="s">
@@ -1798,10 +1798,10 @@
       </c>
     </row>
     <row r="51" spans="1:3" ht="27.75" x14ac:dyDescent="0.4">
-      <c r="A51" s="9" t="s">
+      <c r="A51" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B51" s="9" t="s">
+      <c r="B51" s="8" t="s">
         <v>121</v>
       </c>
       <c r="C51" s="3" t="s">
@@ -1809,75 +1809,75 @@
       </c>
     </row>
     <row r="52" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="9" t="s">
+      <c r="A52" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="C52" s="10" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A53" s="9" t="s">
+      <c r="A53" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B53" s="9" t="s">
+      <c r="B53" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="C53" s="7"/>
+      <c r="C53" s="10"/>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A54" s="9" t="s">
+      <c r="A54" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B54" s="9" t="s">
+      <c r="B54" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="C54" s="7"/>
+      <c r="C54" s="10"/>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A55" s="9" t="s">
+      <c r="A55" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B55" s="9" t="s">
+      <c r="B55" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="C55" s="7"/>
+      <c r="C55" s="10"/>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A56" s="9" t="s">
+      <c r="A56" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B56" s="9" t="s">
+      <c r="B56" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="C56" s="7"/>
+      <c r="C56" s="10"/>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A57" s="9" t="s">
+      <c r="A57" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B57" s="9" t="s">
+      <c r="B57" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="C57" s="7"/>
+      <c r="C57" s="10"/>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A58" s="9" t="s">
+      <c r="A58" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B58" s="9" t="s">
+      <c r="B58" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="C58" s="7"/>
+      <c r="C58" s="10"/>
     </row>
     <row r="59" spans="1:3" ht="41.65" x14ac:dyDescent="0.4">
-      <c r="A59" s="9" t="s">
+      <c r="A59" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B59" s="9" t="s">
+      <c r="B59" s="8" t="s">
         <v>129</v>
       </c>
       <c r="C59" s="3" t="s">
@@ -1885,10 +1885,10 @@
       </c>
     </row>
     <row r="60" spans="1:3" ht="27.75" x14ac:dyDescent="0.4">
-      <c r="A60" s="9" t="s">
+      <c r="A60" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B60" s="9" t="s">
+      <c r="B60" s="8" t="s">
         <v>130</v>
       </c>
       <c r="C60" s="3" t="s">
@@ -1896,10 +1896,10 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="27.75" x14ac:dyDescent="0.4">
-      <c r="A61" s="9" t="s">
+      <c r="A61" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B61" s="9" t="s">
+      <c r="B61" s="8" t="s">
         <v>131</v>
       </c>
       <c r="C61" s="3" t="s">
@@ -1913,7 +1913,7 @@
       <c r="B62" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C62" s="7" t="s">
+      <c r="C62" s="10" t="s">
         <v>137</v>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       <c r="B63" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="C63" s="7"/>
+      <c r="C63" s="10"/>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A64" s="3" t="s">
@@ -1933,7 +1933,7 @@
       <c r="B64" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C64" s="7"/>
+      <c r="C64" s="10"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A65" s="3" t="s">
@@ -1942,7 +1942,7 @@
       <c r="B65" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="C65" s="7"/>
+      <c r="C65" s="10"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A66" s="3" t="s">
@@ -1951,7 +1951,7 @@
       <c r="B66" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C66" s="7"/>
+      <c r="C66" s="10"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A67" s="3" t="s">
@@ -1960,7 +1960,7 @@
       <c r="B67" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C67" s="7"/>
+      <c r="C67" s="10"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A68" s="3" t="s">
@@ -1969,7 +1969,7 @@
       <c r="B68" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="C68" s="7"/>
+      <c r="C68" s="10"/>
     </row>
     <row r="69" spans="1:5" ht="41.65" x14ac:dyDescent="0.4">
       <c r="A69" s="3" t="s">
@@ -1978,7 +1978,7 @@
       <c r="B69" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="C69" s="9" t="s">
+      <c r="C69" s="8" t="s">
         <v>138</v>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       <c r="B70" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="C70" s="9" t="s">
+      <c r="C70" s="8" t="s">
         <v>139</v>
       </c>
     </row>
@@ -2000,15 +2000,15 @@
       <c r="B71" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="C71" s="9" t="s">
+      <c r="C71" s="8" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="8" t="s">
+      <c r="A72" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B72" s="9" t="s">
+      <c r="B72" s="8" t="s">
         <v>132</v>
       </c>
       <c r="C72" s="3" t="s">
@@ -2016,20 +2016,20 @@
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A73" s="8" t="s">
+      <c r="A73" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B73" s="9" t="s">
+      <c r="B73" s="8" t="s">
         <v>133</v>
       </c>
       <c r="C73" s="3"/>
       <c r="E73" s="3"/>
     </row>
     <row r="74" spans="1:5" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A74" s="8" t="s">
+      <c r="A74" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B74" s="9" t="s">
+      <c r="B74" s="8" t="s">
         <v>134</v>
       </c>
       <c r="C74" s="3" t="s">
@@ -2038,10 +2038,10 @@
       <c r="E74" s="3"/>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A75" s="8" t="s">
+      <c r="A75" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B75" s="9" t="s">
+      <c r="B75" s="8" t="s">
         <v>135</v>
       </c>
       <c r="C75" s="3"/>
@@ -2053,7 +2053,7 @@
       <c r="B76" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="C76" s="5" t="s">
+      <c r="C76" s="9" t="s">
         <v>145</v>
       </c>
     </row>
@@ -2061,16 +2061,16 @@
       <c r="A77" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B77" s="9" t="s">
+      <c r="B77" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="C77" s="5"/>
+      <c r="C77" s="9"/>
     </row>
     <row r="78" spans="1:5" ht="41.65" x14ac:dyDescent="0.4">
       <c r="A78" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B78" s="9" t="s">
+      <c r="B78" s="8" t="s">
         <v>146</v>
       </c>
       <c r="C78" s="6" t="s">
@@ -2081,10 +2081,10 @@
       <c r="A79" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B79" s="9" t="s">
+      <c r="B79" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="C79" s="7" t="s">
+      <c r="C79" s="10" t="s">
         <v>150</v>
       </c>
     </row>
@@ -2092,19 +2092,19 @@
       <c r="A80" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B80" s="9" t="s">
+      <c r="B80" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="C80" s="7"/>
+      <c r="C80" s="10"/>
     </row>
     <row r="81" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B81" s="9" t="s">
+      <c r="B81" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="C81" s="5" t="s">
+      <c r="C81" s="9" t="s">
         <v>190</v>
       </c>
     </row>
@@ -2112,61 +2112,61 @@
       <c r="A82" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B82" s="9" t="s">
+      <c r="B82" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="C82" s="5"/>
+      <c r="C82" s="9"/>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A83" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="B83" s="9" t="s">
+      <c r="B83" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="C83" s="5"/>
+      <c r="C83" s="9"/>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A84" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="B84" s="9" t="s">
+      <c r="B84" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="C84" s="5"/>
+      <c r="C84" s="9"/>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A85" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="B85" s="9" t="s">
+      <c r="B85" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="C85" s="5"/>
+      <c r="C85" s="9"/>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A86" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="B86" s="9" t="s">
+      <c r="B86" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="C86" s="5"/>
+      <c r="C86" s="9"/>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A87" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="B87" s="9" t="s">
+      <c r="B87" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="C87" s="5"/>
+      <c r="C87" s="9"/>
     </row>
     <row r="88" spans="1:3" ht="27.75" x14ac:dyDescent="0.4">
       <c r="A88" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="B88" s="9" t="s">
+      <c r="B88" s="8" t="s">
         <v>184</v>
       </c>
       <c r="C88" s="6" t="s">
@@ -2177,7 +2177,7 @@
       <c r="A89" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="B89" s="9" t="s">
+      <c r="B89" s="8" t="s">
         <v>185</v>
       </c>
       <c r="C89" s="6" t="s">
@@ -2188,7 +2188,7 @@
       <c r="A90" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="B90" s="9" t="s">
+      <c r="B90" s="8" t="s">
         <v>198</v>
       </c>
       <c r="C90" s="6"/>
@@ -2197,7 +2197,7 @@
       <c r="A91" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="B91" s="9" t="s">
+      <c r="B91" s="8" t="s">
         <v>202</v>
       </c>
       <c r="C91" s="6"/>
@@ -2206,7 +2206,7 @@
       <c r="A92" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="B92" s="9" t="s">
+      <c r="B92" s="8" t="s">
         <v>204</v>
       </c>
       <c r="C92" s="6"/>
@@ -2215,10 +2215,10 @@
       <c r="A93" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="B93" s="9" t="s">
+      <c r="B93" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="C93" s="5" t="s">
+      <c r="C93" s="9" t="s">
         <v>192</v>
       </c>
     </row>
@@ -2226,19 +2226,19 @@
       <c r="A94" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="B94" s="9" t="s">
+      <c r="B94" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="C94" s="5"/>
+      <c r="C94" s="9"/>
     </row>
     <row r="95" spans="1:3" ht="55.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="B95" s="9" t="s">
+      <c r="B95" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="C95" s="5" t="s">
+      <c r="C95" s="9" t="s">
         <v>206</v>
       </c>
     </row>
@@ -2246,52 +2246,52 @@
       <c r="A96" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="B96" s="9" t="s">
+      <c r="B96" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C96" s="5"/>
+      <c r="C96" s="9"/>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A97" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="B97" s="9" t="s">
+      <c r="B97" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="C97" s="5"/>
+      <c r="C97" s="9"/>
     </row>
     <row r="98" spans="1:3" ht="27.75" x14ac:dyDescent="0.4">
       <c r="A98" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="B98" s="9" t="s">
+      <c r="B98" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="C98" s="5"/>
+      <c r="C98" s="9"/>
     </row>
     <row r="99" spans="1:3" ht="27.75" x14ac:dyDescent="0.4">
       <c r="A99" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="B99" s="9" t="s">
+      <c r="B99" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="C99" s="5"/>
+      <c r="C99" s="9"/>
     </row>
     <row r="100" spans="1:3" ht="27.75" x14ac:dyDescent="0.4">
       <c r="A100" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="B100" s="9" t="s">
+      <c r="B100" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="C100" s="5"/>
+      <c r="C100" s="9"/>
     </row>
     <row r="101" spans="1:3" ht="41.65" x14ac:dyDescent="0.4">
       <c r="A101" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="B101" s="9" t="s">
+      <c r="B101" s="8" t="s">
         <v>214</v>
       </c>
       <c r="C101" s="6" t="s">
@@ -2302,7 +2302,7 @@
       <c r="A102" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="B102" s="9" t="s">
+      <c r="B102" s="8" t="s">
         <v>215</v>
       </c>
       <c r="C102" s="6"/>
@@ -2311,10 +2311,10 @@
       <c r="A103" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="B103" s="9" t="s">
+      <c r="B103" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="C103" s="10" t="s">
+      <c r="C103" s="5" t="s">
         <v>232</v>
       </c>
     </row>
@@ -2322,10 +2322,10 @@
       <c r="A104" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="B104" s="9" t="s">
+      <c r="B104" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="C104" s="10" t="s">
+      <c r="C104" s="5" t="s">
         <v>234</v>
       </c>
     </row>
@@ -2333,10 +2333,10 @@
       <c r="A105" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="B105" s="9" t="s">
+      <c r="B105" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="C105" s="10" t="s">
+      <c r="C105" s="5" t="s">
         <v>236</v>
       </c>
     </row>
@@ -2344,10 +2344,10 @@
       <c r="A106" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="B106" s="9" t="s">
+      <c r="B106" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="C106" s="10" t="s">
+      <c r="C106" s="5" t="s">
         <v>238</v>
       </c>
     </row>
@@ -2355,10 +2355,10 @@
       <c r="A107" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="B107" s="9" t="s">
+      <c r="B107" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="C107" s="10" t="s">
+      <c r="C107" s="5" t="s">
         <v>240</v>
       </c>
     </row>
@@ -2366,10 +2366,10 @@
       <c r="A108" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="B108" s="9" t="s">
+      <c r="B108" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="C108" s="10" t="s">
+      <c r="C108" s="5" t="s">
         <v>242</v>
       </c>
     </row>
@@ -2377,10 +2377,10 @@
       <c r="A109" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="B109" s="9" t="s">
+      <c r="B109" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="C109" s="10" t="s">
+      <c r="C109" s="5" t="s">
         <v>244</v>
       </c>
     </row>
@@ -2388,10 +2388,10 @@
       <c r="A110" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B110" s="9" t="s">
+      <c r="B110" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="C110" s="10" t="s">
+      <c r="C110" s="5" t="s">
         <v>246</v>
       </c>
     </row>
@@ -2399,10 +2399,10 @@
       <c r="A111" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="B111" s="9" t="s">
+      <c r="B111" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="C111" s="10" t="s">
+      <c r="C111" s="5" t="s">
         <v>247</v>
       </c>
     </row>
@@ -2410,10 +2410,10 @@
       <c r="A112" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="B112" s="9" t="s">
+      <c r="B112" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="C112" s="10" t="s">
+      <c r="C112" s="5" t="s">
         <v>250</v>
       </c>
     </row>
@@ -2484,18 +2484,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C52:C58"/>
+    <mergeCell ref="C2:C8"/>
+    <mergeCell ref="C12:C18"/>
+    <mergeCell ref="C22:C28"/>
+    <mergeCell ref="C32:C38"/>
+    <mergeCell ref="C42:C48"/>
     <mergeCell ref="C95:C100"/>
     <mergeCell ref="C76:C77"/>
     <mergeCell ref="C79:C80"/>
     <mergeCell ref="C62:C68"/>
     <mergeCell ref="C81:C87"/>
     <mergeCell ref="C93:C94"/>
-    <mergeCell ref="C2:C8"/>
-    <mergeCell ref="C12:C18"/>
-    <mergeCell ref="C22:C28"/>
-    <mergeCell ref="C32:C38"/>
-    <mergeCell ref="C42:C48"/>
-    <mergeCell ref="C52:C58"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
